--- a/Laporan_Lengkap_Usaha_Ayam.xlsx
+++ b/Laporan_Lengkap_Usaha_Ayam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/de310d021c6f6b02/ドキュメント/kuliah sem 7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DF9E9B8DF4CEBD2A0B41D75333DB74A6377AAE73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE70A9A2-29F8-46F9-A613-51AA8C6E5829}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_DF9E9B8DF4CEBD2A0B41D75333DB74A6377AAE73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5D1D3E-BB0A-4C9A-AAD1-633B2C2662A7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameter Input" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,13 @@
     <sheet name="Simulasi Harga Pakan" sheetId="5" r:id="rId5"/>
     <sheet name="Simulasi Harga Jual" sheetId="6" r:id="rId6"/>
     <sheet name="Sensitivitas Jumlah Ayam" sheetId="7" r:id="rId7"/>
-    <sheet name="Grafik &amp; Visualisasi" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>Parameter</t>
   </si>
@@ -204,22 +203,13 @@
   </si>
   <si>
     <t>Harga Jual Baru (Rp)</t>
-  </si>
-  <si>
-    <t>Visualisasi Analisis Profit</t>
-  </si>
-  <si>
-    <t>Grafik: Target Profit 10Jt</t>
-  </si>
-  <si>
-    <t>Grafik: Profit Maksimum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,14 +220,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -285,11 +267,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -305,155 +285,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>152156</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>113322</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="target profit 10jt.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="447675" y="1143000"/>
-          <a:ext cx="11896481" cy="6637947"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>595312</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>379164</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Gambar 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECE9DC4-6EC9-1088-EEF2-EB3E7CF15A68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12977812" y="1143000"/>
-          <a:ext cx="9689852" cy="6691312"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>595312</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>60971</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Gambar 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5039DB81-9714-D37F-08DA-C194CC98FF51}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23502937" y="1143000"/>
-          <a:ext cx="6643688" cy="10586096"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2120,31 +1951,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>